--- a/template/北一區週報_優化.xlsx
+++ b/template/北一區週報_優化.xlsx
@@ -13138,7 +13138,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AF38"/>
+  <dimension ref="A1:AH38"/>
   <sheetFormatPr baseColWidth="10" defaultColWidth="9" defaultRowHeight="14"/>
   <cols>
     <col width="18" customWidth="1" style="83" min="1" max="1"/>
@@ -13191,6 +13191,8 @@
       <c r="AD1" s="135" t="n"/>
       <c r="AE1" s="135" t="n"/>
       <c r="AF1" s="135" t="n"/>
+      <c r="AG1" s="135" t="n"/>
+      <c r="AH1" s="135" t="n"/>
     </row>
     <row r="2" ht="36" customHeight="1" s="83">
       <c r="A2" s="72" t="n"/>
@@ -13240,51 +13242,61 @@
       <c r="U2" s="72" t="n"/>
       <c r="V2" s="72" t="inlineStr">
         <is>
+          <t>3PP搭售率(未加Care)</t>
+        </is>
+      </c>
+      <c r="W2" s="72" t="inlineStr">
+        <is>
+          <t>3PP搭售率(未加Care)</t>
+        </is>
+      </c>
+      <c r="X2" s="72" t="inlineStr">
+        <is>
+          <t>SA Care搭售率</t>
+        </is>
+      </c>
+      <c r="Y2" s="72" t="inlineStr">
+        <is>
+          <t>SA Care搭售率</t>
+        </is>
+      </c>
+      <c r="Z2" s="72" t="inlineStr">
+        <is>
+          <t>AC搭售率</t>
+        </is>
+      </c>
+      <c r="AA2" s="72" t="inlineStr">
+        <is>
+          <t>AC搭售率</t>
+        </is>
+      </c>
+      <c r="AB2" s="72" t="inlineStr">
+        <is>
+          <t>禮券金額</t>
+        </is>
+      </c>
+      <c r="AC2" s="72" t="n"/>
+      <c r="AD2" s="72" t="n"/>
+      <c r="AE2" s="72" t="inlineStr">
+        <is>
           <t>總業績差異</t>
         </is>
       </c>
-      <c r="W2" s="72" t="inlineStr">
+      <c r="AF2" s="72" t="inlineStr">
         <is>
           <t>3PP(未加SA Care)差異</t>
         </is>
       </c>
-      <c r="X2" s="72" t="inlineStr">
+      <c r="AG2" s="72" t="inlineStr">
         <is>
           <t>SA Care</t>
         </is>
       </c>
-      <c r="Y2" s="72" t="inlineStr">
+      <c r="AH2" s="72" t="inlineStr">
         <is>
           <t>AC</t>
         </is>
       </c>
-      <c r="Z2" s="72" t="inlineStr">
-        <is>
-          <t>3PP搭售率(未加Care)</t>
-        </is>
-      </c>
-      <c r="AA2" s="72" t="inlineStr">
-        <is>
-          <t>3PP搭售率(未加Care)</t>
-        </is>
-      </c>
-      <c r="AB2" s="72" t="inlineStr">
-        <is>
-          <t>SA Care搭售率</t>
-        </is>
-      </c>
-      <c r="AC2" s="72" t="inlineStr">
-        <is>
-          <t>SA Care搭售率</t>
-        </is>
-      </c>
-      <c r="AD2" s="72" t="inlineStr">
-        <is>
-          <t>禮券金額</t>
-        </is>
-      </c>
-      <c r="AE2" s="72" t="n"/>
-      <c r="AF2" s="72" t="n"/>
     </row>
     <row r="3" ht="42" customHeight="1" s="83">
       <c r="A3" s="86" t="n"/>
@@ -13404,49 +13416,61 @@
           <t>較上月比</t>
         </is>
       </c>
-      <c r="V3" s="86" t="n"/>
-      <c r="W3" s="86" t="n"/>
-      <c r="X3" s="86" t="n"/>
-      <c r="Y3" s="86" t="n"/>
-      <c r="Z3" s="70" t="inlineStr">
+      <c r="V3" s="70" t="inlineStr">
         <is>
           <t>3PP搭售率
 上月</t>
         </is>
       </c>
-      <c r="AA3" s="71" t="inlineStr">
+      <c r="W3" s="71" t="inlineStr">
         <is>
           <t>3PP搭售率
 本月</t>
         </is>
       </c>
-      <c r="AB3" s="75" t="inlineStr">
+      <c r="X3" s="75" t="inlineStr">
         <is>
           <t>SACARE搭售率
 上月</t>
         </is>
       </c>
-      <c r="AC3" s="76" t="inlineStr">
+      <c r="Y3" s="76" t="inlineStr">
         <is>
           <t>SACARE搭售率
 本月</t>
         </is>
       </c>
-      <c r="AD3" s="39" t="inlineStr">
+      <c r="Z3" s="75" t="inlineStr">
+        <is>
+          <t>AC搭售率
+上月</t>
+        </is>
+      </c>
+      <c r="AA3" s="76" t="inlineStr">
+        <is>
+          <t>AC搭售率
+本月</t>
+        </is>
+      </c>
+      <c r="AB3" s="39" t="inlineStr">
         <is>
           <t>上月</t>
         </is>
       </c>
-      <c r="AE3" s="40" t="inlineStr">
+      <c r="AC3" s="40" t="inlineStr">
         <is>
           <t>本月</t>
         </is>
       </c>
-      <c r="AF3" s="86" t="inlineStr">
+      <c r="AD3" s="86" t="inlineStr">
         <is>
           <t>較上週比</t>
         </is>
       </c>
+      <c r="AE3" s="86" t="n"/>
+      <c r="AF3" s="86" t="n"/>
+      <c r="AG3" s="86" t="n"/>
+      <c r="AH3" s="86" t="n"/>
     </row>
     <row r="4" ht="20" customHeight="1" s="83">
       <c r="A4" s="73" t="inlineStr">
@@ -13510,35 +13534,41 @@
       <c r="U4" s="74" t="n">
         <v>0</v>
       </c>
-      <c r="V4" s="123" t="n">
-        <v>0</v>
-      </c>
-      <c r="W4" s="123" t="n">
-        <v>0</v>
-      </c>
-      <c r="X4" s="123" t="n"/>
-      <c r="Y4" s="123" t="n"/>
+      <c r="V4" s="44" t="n">
+        <v>0</v>
+      </c>
+      <c r="W4" s="44" t="n">
+        <v>0</v>
+      </c>
+      <c r="X4" s="44" t="n">
+        <v>0</v>
+      </c>
+      <c r="Y4" s="44" t="n">
+        <v>0</v>
+      </c>
       <c r="Z4" s="44" t="n">
         <v>0</v>
       </c>
       <c r="AA4" s="44" t="n">
         <v>0</v>
       </c>
-      <c r="AB4" s="44" t="n">
-        <v>0</v>
-      </c>
-      <c r="AC4" s="44" t="n">
-        <v>0</v>
-      </c>
-      <c r="AD4" s="123" t="n">
+      <c r="AB4" s="123" t="n">
+        <v>0</v>
+      </c>
+      <c r="AC4" s="123" t="n">
+        <v>0</v>
+      </c>
+      <c r="AD4" s="74" t="n">
         <v>0</v>
       </c>
       <c r="AE4" s="123" t="n">
         <v>0</v>
       </c>
-      <c r="AF4" s="74" t="n">
-        <v>0</v>
-      </c>
+      <c r="AF4" s="123" t="n">
+        <v>0</v>
+      </c>
+      <c r="AG4" s="123" t="n"/>
+      <c r="AH4" s="123" t="n"/>
     </row>
     <row r="5" ht="20" customHeight="1" s="83">
       <c r="A5" s="73" t="inlineStr">
@@ -13602,35 +13632,41 @@
       <c r="U5" s="74" t="n">
         <v>0</v>
       </c>
-      <c r="V5" s="124" t="n">
-        <v>0</v>
-      </c>
-      <c r="W5" s="124" t="n">
-        <v>0</v>
-      </c>
-      <c r="X5" s="124" t="n"/>
-      <c r="Y5" s="124" t="n"/>
+      <c r="V5" s="46" t="n">
+        <v>0</v>
+      </c>
+      <c r="W5" s="46" t="n">
+        <v>0</v>
+      </c>
+      <c r="X5" s="46" t="n">
+        <v>0</v>
+      </c>
+      <c r="Y5" s="46" t="n">
+        <v>0</v>
+      </c>
       <c r="Z5" s="46" t="n">
         <v>0</v>
       </c>
       <c r="AA5" s="46" t="n">
         <v>0</v>
       </c>
-      <c r="AB5" s="46" t="n">
-        <v>0</v>
-      </c>
-      <c r="AC5" s="46" t="n">
-        <v>0</v>
-      </c>
-      <c r="AD5" s="124" t="n">
+      <c r="AB5" s="124" t="n">
+        <v>0</v>
+      </c>
+      <c r="AC5" s="124" t="n">
+        <v>0</v>
+      </c>
+      <c r="AD5" s="74" t="n">
         <v>0</v>
       </c>
       <c r="AE5" s="124" t="n">
         <v>0</v>
       </c>
-      <c r="AF5" s="74" t="n">
-        <v>0</v>
-      </c>
+      <c r="AF5" s="124" t="n">
+        <v>0</v>
+      </c>
+      <c r="AG5" s="124" t="n"/>
+      <c r="AH5" s="124" t="n"/>
     </row>
     <row r="6" ht="20" customHeight="1" s="83">
       <c r="A6" s="73" t="inlineStr">
@@ -13694,35 +13730,41 @@
       <c r="U6" s="74" t="n">
         <v>0</v>
       </c>
-      <c r="V6" s="123" t="n">
-        <v>0</v>
-      </c>
-      <c r="W6" s="123" t="n">
-        <v>0</v>
-      </c>
-      <c r="X6" s="123" t="n"/>
-      <c r="Y6" s="123" t="n"/>
+      <c r="V6" s="44" t="n">
+        <v>0</v>
+      </c>
+      <c r="W6" s="44" t="n">
+        <v>0</v>
+      </c>
+      <c r="X6" s="44" t="n">
+        <v>0</v>
+      </c>
+      <c r="Y6" s="44" t="n">
+        <v>0</v>
+      </c>
       <c r="Z6" s="44" t="n">
         <v>0</v>
       </c>
       <c r="AA6" s="44" t="n">
         <v>0</v>
       </c>
-      <c r="AB6" s="44" t="n">
-        <v>0</v>
-      </c>
-      <c r="AC6" s="44" t="n">
-        <v>0</v>
-      </c>
-      <c r="AD6" s="123" t="n">
+      <c r="AB6" s="123" t="n">
+        <v>0</v>
+      </c>
+      <c r="AC6" s="123" t="n">
+        <v>0</v>
+      </c>
+      <c r="AD6" s="74" t="n">
         <v>0</v>
       </c>
       <c r="AE6" s="123" t="n">
         <v>0</v>
       </c>
-      <c r="AF6" s="74" t="n">
-        <v>0</v>
-      </c>
+      <c r="AF6" s="123" t="n">
+        <v>0</v>
+      </c>
+      <c r="AG6" s="123" t="n"/>
+      <c r="AH6" s="123" t="n"/>
     </row>
     <row r="7" ht="20" customHeight="1" s="83">
       <c r="A7" s="73" t="inlineStr">
@@ -13786,35 +13828,41 @@
       <c r="U7" s="74" t="n">
         <v>0</v>
       </c>
-      <c r="V7" s="124" t="n">
-        <v>0</v>
-      </c>
-      <c r="W7" s="124" t="n">
-        <v>0</v>
-      </c>
-      <c r="X7" s="124" t="n"/>
-      <c r="Y7" s="124" t="n"/>
+      <c r="V7" s="46" t="n">
+        <v>0</v>
+      </c>
+      <c r="W7" s="46" t="n">
+        <v>0</v>
+      </c>
+      <c r="X7" s="46" t="n">
+        <v>0</v>
+      </c>
+      <c r="Y7" s="46" t="n">
+        <v>0</v>
+      </c>
       <c r="Z7" s="46" t="n">
         <v>0</v>
       </c>
       <c r="AA7" s="46" t="n">
         <v>0</v>
       </c>
-      <c r="AB7" s="46" t="n">
-        <v>0</v>
-      </c>
-      <c r="AC7" s="46" t="n">
-        <v>0</v>
-      </c>
-      <c r="AD7" s="124" t="n">
+      <c r="AB7" s="124" t="n">
+        <v>0</v>
+      </c>
+      <c r="AC7" s="124" t="n">
+        <v>0</v>
+      </c>
+      <c r="AD7" s="74" t="n">
         <v>0</v>
       </c>
       <c r="AE7" s="124" t="n">
         <v>0</v>
       </c>
-      <c r="AF7" s="74" t="n">
-        <v>0</v>
-      </c>
+      <c r="AF7" s="124" t="n">
+        <v>0</v>
+      </c>
+      <c r="AG7" s="124" t="n"/>
+      <c r="AH7" s="124" t="n"/>
     </row>
     <row r="8" ht="20" customHeight="1" s="83">
       <c r="A8" s="73" t="inlineStr">
@@ -13878,35 +13926,41 @@
       <c r="U8" s="74" t="n">
         <v>0</v>
       </c>
-      <c r="V8" s="123" t="n">
-        <v>0</v>
-      </c>
-      <c r="W8" s="123" t="n">
-        <v>0</v>
-      </c>
-      <c r="X8" s="123" t="n"/>
-      <c r="Y8" s="123" t="n"/>
+      <c r="V8" s="44" t="n">
+        <v>0</v>
+      </c>
+      <c r="W8" s="44" t="n">
+        <v>0</v>
+      </c>
+      <c r="X8" s="44" t="n">
+        <v>0</v>
+      </c>
+      <c r="Y8" s="44" t="n">
+        <v>0</v>
+      </c>
       <c r="Z8" s="44" t="n">
         <v>0</v>
       </c>
       <c r="AA8" s="44" t="n">
         <v>0</v>
       </c>
-      <c r="AB8" s="44" t="n">
-        <v>0</v>
-      </c>
-      <c r="AC8" s="44" t="n">
-        <v>0</v>
-      </c>
-      <c r="AD8" s="123" t="n">
+      <c r="AB8" s="123" t="n">
+        <v>0</v>
+      </c>
+      <c r="AC8" s="123" t="n">
+        <v>0</v>
+      </c>
+      <c r="AD8" s="74" t="n">
         <v>0</v>
       </c>
       <c r="AE8" s="123" t="n">
         <v>0</v>
       </c>
-      <c r="AF8" s="74" t="n">
-        <v>0</v>
-      </c>
+      <c r="AF8" s="123" t="n">
+        <v>0</v>
+      </c>
+      <c r="AG8" s="123" t="n"/>
+      <c r="AH8" s="123" t="n"/>
     </row>
     <row r="9" ht="20" customHeight="1" s="83">
       <c r="A9" s="73" t="inlineStr">
@@ -13970,35 +14024,41 @@
       <c r="U9" s="74" t="n">
         <v>0</v>
       </c>
-      <c r="V9" s="124" t="n">
-        <v>0</v>
-      </c>
-      <c r="W9" s="124" t="n">
-        <v>0</v>
-      </c>
-      <c r="X9" s="124" t="n"/>
-      <c r="Y9" s="124" t="n"/>
+      <c r="V9" s="46" t="n">
+        <v>0</v>
+      </c>
+      <c r="W9" s="46" t="n">
+        <v>0</v>
+      </c>
+      <c r="X9" s="46" t="n">
+        <v>0</v>
+      </c>
+      <c r="Y9" s="46" t="n">
+        <v>0</v>
+      </c>
       <c r="Z9" s="46" t="n">
         <v>0</v>
       </c>
       <c r="AA9" s="46" t="n">
         <v>0</v>
       </c>
-      <c r="AB9" s="46" t="n">
-        <v>0</v>
-      </c>
-      <c r="AC9" s="46" t="n">
-        <v>0</v>
-      </c>
-      <c r="AD9" s="124" t="n">
+      <c r="AB9" s="124" t="n">
+        <v>0</v>
+      </c>
+      <c r="AC9" s="124" t="n">
+        <v>0</v>
+      </c>
+      <c r="AD9" s="74" t="n">
         <v>0</v>
       </c>
       <c r="AE9" s="124" t="n">
         <v>0</v>
       </c>
-      <c r="AF9" s="74" t="n">
-        <v>0</v>
-      </c>
+      <c r="AF9" s="124" t="n">
+        <v>0</v>
+      </c>
+      <c r="AG9" s="124" t="n"/>
+      <c r="AH9" s="124" t="n"/>
     </row>
     <row r="10" ht="20" customHeight="1" s="83">
       <c r="A10" s="47" t="inlineStr">
@@ -14062,35 +14122,41 @@
       <c r="U10" s="49" t="n">
         <v>0</v>
       </c>
-      <c r="V10" s="125" t="n">
-        <v>0</v>
-      </c>
-      <c r="W10" s="125" t="n">
-        <v>0</v>
-      </c>
-      <c r="X10" s="125" t="n"/>
-      <c r="Y10" s="125" t="n"/>
+      <c r="V10" s="49" t="n">
+        <v>0</v>
+      </c>
+      <c r="W10" s="49" t="n">
+        <v>0</v>
+      </c>
+      <c r="X10" s="49" t="n">
+        <v>0</v>
+      </c>
+      <c r="Y10" s="49" t="n">
+        <v>0</v>
+      </c>
       <c r="Z10" s="49" t="n">
         <v>0</v>
       </c>
       <c r="AA10" s="49" t="n">
         <v>0</v>
       </c>
-      <c r="AB10" s="49" t="n">
-        <v>0</v>
-      </c>
-      <c r="AC10" s="49" t="n">
-        <v>0</v>
-      </c>
-      <c r="AD10" s="125" t="n">
+      <c r="AB10" s="125" t="n">
+        <v>0</v>
+      </c>
+      <c r="AC10" s="125" t="n">
+        <v>0</v>
+      </c>
+      <c r="AD10" s="49" t="n">
         <v>0</v>
       </c>
       <c r="AE10" s="125" t="n">
         <v>0</v>
       </c>
-      <c r="AF10" s="49" t="n">
-        <v>0</v>
-      </c>
+      <c r="AF10" s="125" t="n">
+        <v>0</v>
+      </c>
+      <c r="AG10" s="125" t="n"/>
+      <c r="AH10" s="125" t="n"/>
     </row>
     <row r="12" ht="26" customHeight="1" s="83">
       <c r="A12" s="72" t="n"/>
@@ -16551,7 +16617,7 @@
     </row>
   </sheetData>
   <mergeCells count="2">
-    <mergeCell ref="A1:AF1"/>
+    <mergeCell ref="A1:AH1"/>
     <mergeCell ref="Q13:Q20"/>
   </mergeCells>
   <conditionalFormatting sqref="D12 D14:D19">
@@ -16770,7 +16836,7 @@
       <formula>0</formula>
     </cfRule>
   </conditionalFormatting>
-  <conditionalFormatting sqref="AF4:AF9">
+  <conditionalFormatting sqref="AD4:AD9">
     <cfRule type="cellIs" priority="39" operator="greaterThan" dxfId="3">
       <formula>0</formula>
     </cfRule>
@@ -16778,7 +16844,7 @@
       <formula>0</formula>
     </cfRule>
   </conditionalFormatting>
-  <conditionalFormatting sqref="AF4:AF10">
+  <conditionalFormatting sqref="AD4:AD10">
     <cfRule type="cellIs" priority="41" operator="greaterThan" dxfId="1">
       <formula>0</formula>
     </cfRule>
@@ -16847,6 +16913,8 @@
       <c r="AB1" s="135" t="n"/>
       <c r="AC1" s="135" t="n"/>
       <c r="AD1" s="135" t="n"/>
+      <c r="AE1" s="135" t="n"/>
+      <c r="AF1" s="135" t="n"/>
     </row>
     <row r="2" ht="36" customHeight="1" s="83">
       <c r="A2" s="105" t="n"/>
@@ -16894,51 +16962,61 @@
       <c r="S2" s="105" t="n"/>
       <c r="T2" s="105" t="inlineStr">
         <is>
+          <t>3PP搭售率(未加Care)</t>
+        </is>
+      </c>
+      <c r="U2" s="105" t="inlineStr">
+        <is>
+          <t>3PP搭售率(未加Care)</t>
+        </is>
+      </c>
+      <c r="V2" s="105" t="inlineStr">
+        <is>
+          <t>SA Care搭售率</t>
+        </is>
+      </c>
+      <c r="W2" s="105" t="inlineStr">
+        <is>
+          <t>SA Care搭售率</t>
+        </is>
+      </c>
+      <c r="X2" s="105" t="inlineStr">
+        <is>
+          <t>AC搭售率</t>
+        </is>
+      </c>
+      <c r="Y2" s="105" t="inlineStr">
+        <is>
+          <t>AC搭售率</t>
+        </is>
+      </c>
+      <c r="Z2" s="105" t="inlineStr">
+        <is>
+          <t>禮券金額</t>
+        </is>
+      </c>
+      <c r="AA2" s="105" t="n"/>
+      <c r="AB2" s="105" t="n"/>
+      <c r="AC2" s="105" t="inlineStr">
+        <is>
           <t>總業績差異</t>
         </is>
       </c>
-      <c r="U2" s="105" t="inlineStr">
+      <c r="AD2" s="105" t="inlineStr">
         <is>
           <t>3PP(未加SA Care)差異</t>
         </is>
       </c>
-      <c r="V2" s="105" t="inlineStr">
+      <c r="AE2" s="105" t="inlineStr">
         <is>
           <t>SA Care</t>
         </is>
       </c>
-      <c r="W2" s="105" t="inlineStr">
+      <c r="AF2" s="105" t="inlineStr">
         <is>
           <t>AC</t>
         </is>
       </c>
-      <c r="X2" s="105" t="inlineStr">
-        <is>
-          <t>3PP搭售率(未加Care)</t>
-        </is>
-      </c>
-      <c r="Y2" s="105" t="inlineStr">
-        <is>
-          <t>3PP搭售率(未加Care)</t>
-        </is>
-      </c>
-      <c r="Z2" s="105" t="inlineStr">
-        <is>
-          <t>SA Care搭售率</t>
-        </is>
-      </c>
-      <c r="AA2" s="105" t="inlineStr">
-        <is>
-          <t>SA Care搭售率</t>
-        </is>
-      </c>
-      <c r="AB2" s="105" t="inlineStr">
-        <is>
-          <t>禮券金額</t>
-        </is>
-      </c>
-      <c r="AC2" s="105" t="n"/>
-      <c r="AD2" s="105" t="n"/>
     </row>
     <row r="3" ht="52" customHeight="1" s="83">
       <c r="A3" s="86" t="n"/>
@@ -17060,51 +17138,63 @@
           <t>較上週比</t>
         </is>
       </c>
-      <c r="T3" s="86" t="n"/>
-      <c r="U3" s="86" t="n"/>
-      <c r="V3" s="86" t="n"/>
-      <c r="W3" s="86" t="n"/>
-      <c r="X3" s="70" t="inlineStr">
+      <c r="T3" s="70" t="inlineStr">
         <is>
           <t>2025
 04/01~04/18</t>
         </is>
       </c>
-      <c r="Y3" s="71" t="inlineStr">
+      <c r="U3" s="71" t="inlineStr">
         <is>
           <t>2026
 04/01~04/18</t>
         </is>
       </c>
-      <c r="Z3" s="70" t="inlineStr">
+      <c r="V3" s="70" t="inlineStr">
         <is>
           <t>2025
 04/01~04/18</t>
         </is>
       </c>
-      <c r="AA3" s="71" t="inlineStr">
+      <c r="W3" s="71" t="inlineStr">
         <is>
           <t>2026
 04/01~04/18</t>
         </is>
       </c>
-      <c r="AB3" s="70" t="inlineStr">
+      <c r="X3" s="70" t="inlineStr">
         <is>
           <t>2025
 04/01~04/18</t>
         </is>
       </c>
-      <c r="AC3" s="71" t="inlineStr">
+      <c r="Y3" s="71" t="inlineStr">
         <is>
           <t>2026
 04/01~04/18</t>
         </is>
       </c>
-      <c r="AD3" s="86" t="inlineStr">
+      <c r="Z3" s="70" t="inlineStr">
+        <is>
+          <t>2025
+04/01~04/18</t>
+        </is>
+      </c>
+      <c r="AA3" s="71" t="inlineStr">
+        <is>
+          <t>2026
+04/01~04/18</t>
+        </is>
+      </c>
+      <c r="AB3" s="86" t="inlineStr">
         <is>
           <t>較上週比</t>
         </is>
       </c>
+      <c r="AC3" s="86" t="n"/>
+      <c r="AD3" s="86" t="n"/>
+      <c r="AE3" s="86" t="n"/>
+      <c r="AF3" s="86" t="n"/>
     </row>
     <row r="4" ht="20" customHeight="1" s="83">
       <c r="A4" s="41" t="inlineStr">
@@ -17166,35 +17256,41 @@
       <c r="S4" s="43" t="n">
         <v>0</v>
       </c>
-      <c r="T4" s="123" t="n">
-        <v>0</v>
-      </c>
-      <c r="U4" s="123" t="n">
-        <v>0</v>
-      </c>
-      <c r="V4" s="123" t="n"/>
-      <c r="W4" s="123" t="n"/>
+      <c r="T4" s="44" t="n">
+        <v>0</v>
+      </c>
+      <c r="U4" s="44" t="n">
+        <v>0</v>
+      </c>
+      <c r="V4" s="44" t="n">
+        <v>0</v>
+      </c>
+      <c r="W4" s="44" t="n">
+        <v>0</v>
+      </c>
       <c r="X4" s="44" t="n">
         <v>0</v>
       </c>
       <c r="Y4" s="44" t="n">
         <v>0</v>
       </c>
-      <c r="Z4" s="44" t="n">
-        <v>0</v>
-      </c>
-      <c r="AA4" s="44" t="n">
-        <v>0</v>
-      </c>
-      <c r="AB4" s="123" t="n">
+      <c r="Z4" s="123" t="n">
+        <v>0</v>
+      </c>
+      <c r="AA4" s="123" t="n">
+        <v>0</v>
+      </c>
+      <c r="AB4" s="43" t="n">
         <v>0</v>
       </c>
       <c r="AC4" s="123" t="n">
         <v>0</v>
       </c>
-      <c r="AD4" s="43" t="n">
-        <v>0</v>
-      </c>
+      <c r="AD4" s="123" t="n">
+        <v>0</v>
+      </c>
+      <c r="AE4" s="123" t="n"/>
+      <c r="AF4" s="123" t="n"/>
     </row>
     <row r="5" ht="20" customHeight="1" s="83">
       <c r="A5" s="41" t="inlineStr">
@@ -17256,35 +17352,41 @@
       <c r="S5" s="43" t="n">
         <v>0</v>
       </c>
-      <c r="T5" s="124" t="n">
-        <v>0</v>
-      </c>
-      <c r="U5" s="124" t="n">
-        <v>0</v>
-      </c>
-      <c r="V5" s="124" t="n"/>
-      <c r="W5" s="124" t="n"/>
+      <c r="T5" s="46" t="n">
+        <v>0</v>
+      </c>
+      <c r="U5" s="46" t="n">
+        <v>0</v>
+      </c>
+      <c r="V5" s="46" t="n">
+        <v>0</v>
+      </c>
+      <c r="W5" s="46" t="n">
+        <v>0</v>
+      </c>
       <c r="X5" s="46" t="n">
         <v>0</v>
       </c>
       <c r="Y5" s="46" t="n">
         <v>0</v>
       </c>
-      <c r="Z5" s="46" t="n">
-        <v>0</v>
-      </c>
-      <c r="AA5" s="46" t="n">
-        <v>0</v>
-      </c>
-      <c r="AB5" s="124" t="n">
+      <c r="Z5" s="124" t="n">
+        <v>0</v>
+      </c>
+      <c r="AA5" s="124" t="n">
+        <v>0</v>
+      </c>
+      <c r="AB5" s="43" t="n">
         <v>0</v>
       </c>
       <c r="AC5" s="124" t="n">
         <v>0</v>
       </c>
-      <c r="AD5" s="43" t="n">
-        <v>0</v>
-      </c>
+      <c r="AD5" s="124" t="n">
+        <v>0</v>
+      </c>
+      <c r="AE5" s="124" t="n"/>
+      <c r="AF5" s="124" t="n"/>
     </row>
     <row r="6" ht="20" customHeight="1" s="83">
       <c r="A6" s="41" t="inlineStr">
@@ -17346,35 +17448,41 @@
       <c r="S6" s="43" t="n">
         <v>0</v>
       </c>
-      <c r="T6" s="123" t="n">
-        <v>0</v>
-      </c>
-      <c r="U6" s="123" t="n">
-        <v>0</v>
-      </c>
-      <c r="V6" s="123" t="n"/>
-      <c r="W6" s="123" t="n"/>
+      <c r="T6" s="44" t="n">
+        <v>0</v>
+      </c>
+      <c r="U6" s="44" t="n">
+        <v>0</v>
+      </c>
+      <c r="V6" s="44" t="n">
+        <v>0</v>
+      </c>
+      <c r="W6" s="44" t="n">
+        <v>0</v>
+      </c>
       <c r="X6" s="44" t="n">
         <v>0</v>
       </c>
       <c r="Y6" s="44" t="n">
         <v>0</v>
       </c>
-      <c r="Z6" s="44" t="n">
-        <v>0</v>
-      </c>
-      <c r="AA6" s="44" t="n">
-        <v>0</v>
-      </c>
-      <c r="AB6" s="123" t="n">
+      <c r="Z6" s="123" t="n">
+        <v>0</v>
+      </c>
+      <c r="AA6" s="123" t="n">
+        <v>0</v>
+      </c>
+      <c r="AB6" s="43" t="n">
         <v>0</v>
       </c>
       <c r="AC6" s="123" t="n">
         <v>0</v>
       </c>
-      <c r="AD6" s="43" t="n">
-        <v>0</v>
-      </c>
+      <c r="AD6" s="123" t="n">
+        <v>0</v>
+      </c>
+      <c r="AE6" s="123" t="n"/>
+      <c r="AF6" s="123" t="n"/>
     </row>
     <row r="7" ht="20" customHeight="1" s="83">
       <c r="A7" s="41" t="inlineStr">
@@ -17436,35 +17544,41 @@
       <c r="S7" s="43" t="n">
         <v>0</v>
       </c>
-      <c r="T7" s="124" t="n">
-        <v>0</v>
-      </c>
-      <c r="U7" s="124" t="n">
-        <v>0</v>
-      </c>
-      <c r="V7" s="124" t="n"/>
-      <c r="W7" s="124" t="n"/>
+      <c r="T7" s="46" t="n">
+        <v>0</v>
+      </c>
+      <c r="U7" s="46" t="n">
+        <v>0</v>
+      </c>
+      <c r="V7" s="46" t="n">
+        <v>0</v>
+      </c>
+      <c r="W7" s="46" t="n">
+        <v>0</v>
+      </c>
       <c r="X7" s="46" t="n">
         <v>0</v>
       </c>
       <c r="Y7" s="46" t="n">
         <v>0</v>
       </c>
-      <c r="Z7" s="46" t="n">
-        <v>0</v>
-      </c>
-      <c r="AA7" s="46" t="n">
-        <v>0</v>
-      </c>
-      <c r="AB7" s="124" t="n">
+      <c r="Z7" s="124" t="n">
+        <v>0</v>
+      </c>
+      <c r="AA7" s="124" t="n">
+        <v>0</v>
+      </c>
+      <c r="AB7" s="43" t="n">
         <v>0</v>
       </c>
       <c r="AC7" s="124" t="n">
         <v>0</v>
       </c>
-      <c r="AD7" s="43" t="n">
-        <v>0</v>
-      </c>
+      <c r="AD7" s="124" t="n">
+        <v>0</v>
+      </c>
+      <c r="AE7" s="124" t="n"/>
+      <c r="AF7" s="124" t="n"/>
     </row>
     <row r="8" ht="20" customHeight="1" s="83">
       <c r="A8" s="41" t="inlineStr">
@@ -17526,35 +17640,41 @@
       <c r="S8" s="43" t="n">
         <v>0</v>
       </c>
-      <c r="T8" s="123" t="n">
-        <v>0</v>
-      </c>
-      <c r="U8" s="123" t="n">
-        <v>0</v>
-      </c>
-      <c r="V8" s="123" t="n"/>
-      <c r="W8" s="123" t="n"/>
+      <c r="T8" s="44" t="n">
+        <v>0</v>
+      </c>
+      <c r="U8" s="44" t="n">
+        <v>0</v>
+      </c>
+      <c r="V8" s="44" t="n">
+        <v>0</v>
+      </c>
+      <c r="W8" s="44" t="n">
+        <v>0</v>
+      </c>
       <c r="X8" s="44" t="n">
         <v>0</v>
       </c>
       <c r="Y8" s="44" t="n">
         <v>0</v>
       </c>
-      <c r="Z8" s="44" t="n">
-        <v>0</v>
-      </c>
-      <c r="AA8" s="44" t="n">
-        <v>0</v>
-      </c>
-      <c r="AB8" s="123" t="n">
+      <c r="Z8" s="123" t="n">
+        <v>0</v>
+      </c>
+      <c r="AA8" s="123" t="n">
+        <v>0</v>
+      </c>
+      <c r="AB8" s="43" t="n">
         <v>0</v>
       </c>
       <c r="AC8" s="123" t="n">
         <v>0</v>
       </c>
-      <c r="AD8" s="43" t="n">
-        <v>0</v>
-      </c>
+      <c r="AD8" s="123" t="n">
+        <v>0</v>
+      </c>
+      <c r="AE8" s="123" t="n"/>
+      <c r="AF8" s="123" t="n"/>
     </row>
     <row r="9" ht="20" customHeight="1" s="83">
       <c r="A9" s="41" t="inlineStr">
@@ -17616,35 +17736,41 @@
       <c r="S9" s="43" t="n">
         <v>0</v>
       </c>
-      <c r="T9" s="124" t="n">
-        <v>0</v>
-      </c>
-      <c r="U9" s="124" t="n">
-        <v>0</v>
-      </c>
-      <c r="V9" s="124" t="n"/>
-      <c r="W9" s="124" t="n"/>
+      <c r="T9" s="46" t="n">
+        <v>0</v>
+      </c>
+      <c r="U9" s="46" t="n">
+        <v>0</v>
+      </c>
+      <c r="V9" s="46" t="n">
+        <v>0</v>
+      </c>
+      <c r="W9" s="46" t="n">
+        <v>0</v>
+      </c>
       <c r="X9" s="46" t="n">
         <v>0</v>
       </c>
       <c r="Y9" s="46" t="n">
         <v>0</v>
       </c>
-      <c r="Z9" s="46" t="n">
-        <v>0</v>
-      </c>
-      <c r="AA9" s="46" t="n">
-        <v>0</v>
-      </c>
-      <c r="AB9" s="124" t="n">
+      <c r="Z9" s="124" t="n">
+        <v>0</v>
+      </c>
+      <c r="AA9" s="124" t="n">
+        <v>0</v>
+      </c>
+      <c r="AB9" s="43" t="n">
         <v>0</v>
       </c>
       <c r="AC9" s="124" t="n">
         <v>0</v>
       </c>
-      <c r="AD9" s="43" t="n">
-        <v>0</v>
-      </c>
+      <c r="AD9" s="124" t="n">
+        <v>0</v>
+      </c>
+      <c r="AE9" s="124" t="n"/>
+      <c r="AF9" s="124" t="n"/>
     </row>
     <row r="10" ht="20" customHeight="1" s="83">
       <c r="A10" s="47" t="inlineStr">
@@ -17706,35 +17832,41 @@
       <c r="S10" s="49" t="n">
         <v>0</v>
       </c>
-      <c r="T10" s="125" t="n">
-        <v>0</v>
-      </c>
-      <c r="U10" s="125" t="n">
-        <v>0</v>
-      </c>
-      <c r="V10" s="125" t="n"/>
-      <c r="W10" s="125" t="n"/>
+      <c r="T10" s="49" t="n">
+        <v>0</v>
+      </c>
+      <c r="U10" s="49" t="n">
+        <v>0</v>
+      </c>
+      <c r="V10" s="49" t="n">
+        <v>0</v>
+      </c>
+      <c r="W10" s="49" t="n">
+        <v>0</v>
+      </c>
       <c r="X10" s="49" t="n">
         <v>0</v>
       </c>
       <c r="Y10" s="49" t="n">
         <v>0</v>
       </c>
-      <c r="Z10" s="49" t="n">
-        <v>0</v>
-      </c>
-      <c r="AA10" s="49" t="n">
-        <v>0</v>
-      </c>
-      <c r="AB10" s="125" t="n">
+      <c r="Z10" s="125" t="n">
+        <v>0</v>
+      </c>
+      <c r="AA10" s="125" t="n">
+        <v>0</v>
+      </c>
+      <c r="AB10" s="49" t="n">
         <v>0</v>
       </c>
       <c r="AC10" s="125" t="n">
         <v>0</v>
       </c>
-      <c r="AD10" s="49" t="n">
-        <v>0</v>
-      </c>
+      <c r="AD10" s="125" t="n">
+        <v>0</v>
+      </c>
+      <c r="AE10" s="125" t="n"/>
+      <c r="AF10" s="125" t="n"/>
     </row>
     <row r="12" ht="26" customHeight="1" s="83">
       <c r="A12" s="72" t="n"/>
@@ -20195,8 +20327,8 @@
     </row>
   </sheetData>
   <mergeCells count="2">
+    <mergeCell ref="A1:AF1"/>
     <mergeCell ref="Q13:Q20"/>
-    <mergeCell ref="A1:AD1"/>
   </mergeCells>
   <conditionalFormatting sqref="D4:D10">
     <cfRule type="cellIs" priority="77" operator="greaterThan" dxfId="3">
@@ -20414,7 +20546,7 @@
       <formula>0</formula>
     </cfRule>
   </conditionalFormatting>
-  <conditionalFormatting sqref="AD4:AD9">
+  <conditionalFormatting sqref="AB4:AB9">
     <cfRule type="cellIs" priority="73" operator="greaterThan" dxfId="3">
       <formula>0</formula>
     </cfRule>
@@ -20422,7 +20554,7 @@
       <formula>0</formula>
     </cfRule>
   </conditionalFormatting>
-  <conditionalFormatting sqref="AD4:AD10">
+  <conditionalFormatting sqref="AB4:AB10">
     <cfRule type="cellIs" priority="75" operator="greaterThan" dxfId="1">
       <formula>0</formula>
     </cfRule>
@@ -20501,51 +20633,61 @@
       <c r="S2" s="105" t="n"/>
       <c r="T2" s="105" t="inlineStr">
         <is>
+          <t>3PP搭售率(未加Care)</t>
+        </is>
+      </c>
+      <c r="U2" s="105" t="inlineStr">
+        <is>
+          <t>3PP搭售率(未加Care)</t>
+        </is>
+      </c>
+      <c r="V2" s="105" t="inlineStr">
+        <is>
+          <t>SA Care搭售率</t>
+        </is>
+      </c>
+      <c r="W2" s="105" t="inlineStr">
+        <is>
+          <t>SA Care搭售率</t>
+        </is>
+      </c>
+      <c r="X2" s="105" t="inlineStr">
+        <is>
+          <t>AC搭售率</t>
+        </is>
+      </c>
+      <c r="Y2" s="105" t="inlineStr">
+        <is>
+          <t>AC搭售率</t>
+        </is>
+      </c>
+      <c r="Z2" s="105" t="inlineStr">
+        <is>
+          <t>禮券金額</t>
+        </is>
+      </c>
+      <c r="AA2" s="105" t="n"/>
+      <c r="AB2" s="105" t="n"/>
+      <c r="AC2" s="105" t="inlineStr">
+        <is>
           <t>總業績差異</t>
         </is>
       </c>
-      <c r="U2" s="105" t="inlineStr">
+      <c r="AD2" s="105" t="inlineStr">
         <is>
           <t>3PP(未加SA Care)差異</t>
         </is>
       </c>
-      <c r="V2" s="105" t="inlineStr">
+      <c r="AE2" s="105" t="inlineStr">
         <is>
           <t>SA Care</t>
         </is>
       </c>
-      <c r="W2" s="105" t="inlineStr">
+      <c r="AF2" s="105" t="inlineStr">
         <is>
           <t>AC</t>
         </is>
       </c>
-      <c r="X2" s="105" t="inlineStr">
-        <is>
-          <t>3PP搭售率(未加Care)</t>
-        </is>
-      </c>
-      <c r="Y2" s="105" t="inlineStr">
-        <is>
-          <t>3PP搭售率(未加Care)</t>
-        </is>
-      </c>
-      <c r="Z2" s="105" t="inlineStr">
-        <is>
-          <t>SA Care搭售率</t>
-        </is>
-      </c>
-      <c r="AA2" s="105" t="inlineStr">
-        <is>
-          <t>SA Care搭售率</t>
-        </is>
-      </c>
-      <c r="AB2" s="105" t="inlineStr">
-        <is>
-          <t>禮券金額</t>
-        </is>
-      </c>
-      <c r="AC2" s="105" t="n"/>
-      <c r="AD2" s="105" t="n"/>
     </row>
     <row r="3" ht="42" customHeight="1" s="83">
       <c r="A3" s="86" t="n"/>
@@ -20667,51 +20809,63 @@
           <t>較上週比</t>
         </is>
       </c>
-      <c r="T3" s="86" t="n"/>
-      <c r="U3" s="86" t="n"/>
-      <c r="V3" s="86" t="n"/>
-      <c r="W3" s="86" t="n"/>
-      <c r="X3" s="39" t="inlineStr">
+      <c r="T3" s="39" t="inlineStr">
         <is>
           <t>2025
 01/01~04/18</t>
         </is>
       </c>
-      <c r="Y3" s="40" t="inlineStr">
+      <c r="U3" s="40" t="inlineStr">
         <is>
           <t>2026
 01/01~04/18</t>
         </is>
       </c>
-      <c r="Z3" s="39" t="inlineStr">
+      <c r="V3" s="39" t="inlineStr">
         <is>
           <t>2025
 01/01~04/18</t>
         </is>
       </c>
-      <c r="AA3" s="40" t="inlineStr">
+      <c r="W3" s="40" t="inlineStr">
         <is>
           <t>2026
 01/01~04/18</t>
         </is>
       </c>
-      <c r="AB3" s="39" t="inlineStr">
+      <c r="X3" s="39" t="inlineStr">
         <is>
           <t>2025
 01/01~04/18</t>
         </is>
       </c>
-      <c r="AC3" s="40" t="inlineStr">
+      <c r="Y3" s="40" t="inlineStr">
         <is>
           <t>2026
 01/01~04/18</t>
         </is>
       </c>
-      <c r="AD3" s="86" t="inlineStr">
+      <c r="Z3" s="39" t="inlineStr">
+        <is>
+          <t>2025
+01/01~04/18</t>
+        </is>
+      </c>
+      <c r="AA3" s="40" t="inlineStr">
+        <is>
+          <t>2026
+01/01~04/18</t>
+        </is>
+      </c>
+      <c r="AB3" s="86" t="inlineStr">
         <is>
           <t>較上週比</t>
         </is>
       </c>
+      <c r="AC3" s="86" t="n"/>
+      <c r="AD3" s="86" t="n"/>
+      <c r="AE3" s="86" t="n"/>
+      <c r="AF3" s="86" t="n"/>
     </row>
     <row r="4" ht="20" customHeight="1" s="83">
       <c r="A4" s="41" t="inlineStr">
@@ -20773,35 +20927,41 @@
       <c r="S4" s="43" t="n">
         <v>0</v>
       </c>
-      <c r="T4" s="123" t="n">
-        <v>0</v>
-      </c>
-      <c r="U4" s="123" t="n">
-        <v>0</v>
-      </c>
-      <c r="V4" s="123" t="n"/>
-      <c r="W4" s="123" t="n"/>
+      <c r="T4" s="44" t="n">
+        <v>0</v>
+      </c>
+      <c r="U4" s="44" t="n">
+        <v>0</v>
+      </c>
+      <c r="V4" s="44" t="n">
+        <v>0</v>
+      </c>
+      <c r="W4" s="44" t="n">
+        <v>0</v>
+      </c>
       <c r="X4" s="44" t="n">
         <v>0</v>
       </c>
       <c r="Y4" s="44" t="n">
         <v>0</v>
       </c>
-      <c r="Z4" s="44" t="n">
-        <v>0</v>
-      </c>
-      <c r="AA4" s="44" t="n">
-        <v>0</v>
-      </c>
-      <c r="AB4" s="123" t="n">
+      <c r="Z4" s="123" t="n">
+        <v>0</v>
+      </c>
+      <c r="AA4" s="123" t="n">
+        <v>0</v>
+      </c>
+      <c r="AB4" s="43" t="n">
         <v>0</v>
       </c>
       <c r="AC4" s="123" t="n">
         <v>0</v>
       </c>
-      <c r="AD4" s="43" t="n">
-        <v>0</v>
-      </c>
+      <c r="AD4" s="123" t="n">
+        <v>0</v>
+      </c>
+      <c r="AE4" s="123" t="n"/>
+      <c r="AF4" s="123" t="n"/>
     </row>
     <row r="5" ht="20" customHeight="1" s="83">
       <c r="A5" s="41" t="inlineStr">
@@ -20863,35 +21023,41 @@
       <c r="S5" s="43" t="n">
         <v>0</v>
       </c>
-      <c r="T5" s="124" t="n">
-        <v>0</v>
-      </c>
-      <c r="U5" s="124" t="n">
-        <v>0</v>
-      </c>
-      <c r="V5" s="124" t="n"/>
-      <c r="W5" s="124" t="n"/>
+      <c r="T5" s="46" t="n">
+        <v>0</v>
+      </c>
+      <c r="U5" s="46" t="n">
+        <v>0</v>
+      </c>
+      <c r="V5" s="46" t="n">
+        <v>0</v>
+      </c>
+      <c r="W5" s="46" t="n">
+        <v>0</v>
+      </c>
       <c r="X5" s="46" t="n">
         <v>0</v>
       </c>
       <c r="Y5" s="46" t="n">
         <v>0</v>
       </c>
-      <c r="Z5" s="46" t="n">
-        <v>0</v>
-      </c>
-      <c r="AA5" s="46" t="n">
-        <v>0</v>
-      </c>
-      <c r="AB5" s="124" t="n">
+      <c r="Z5" s="124" t="n">
+        <v>0</v>
+      </c>
+      <c r="AA5" s="124" t="n">
+        <v>0</v>
+      </c>
+      <c r="AB5" s="43" t="n">
         <v>0</v>
       </c>
       <c r="AC5" s="124" t="n">
         <v>0</v>
       </c>
-      <c r="AD5" s="43" t="n">
-        <v>0</v>
-      </c>
+      <c r="AD5" s="124" t="n">
+        <v>0</v>
+      </c>
+      <c r="AE5" s="124" t="n"/>
+      <c r="AF5" s="124" t="n"/>
     </row>
     <row r="6" ht="20" customHeight="1" s="83">
       <c r="A6" s="41" t="inlineStr">
@@ -20953,35 +21119,41 @@
       <c r="S6" s="43" t="n">
         <v>0</v>
       </c>
-      <c r="T6" s="123" t="n">
-        <v>0</v>
-      </c>
-      <c r="U6" s="123" t="n">
-        <v>0</v>
-      </c>
-      <c r="V6" s="123" t="n"/>
-      <c r="W6" s="123" t="n"/>
+      <c r="T6" s="44" t="n">
+        <v>0</v>
+      </c>
+      <c r="U6" s="44" t="n">
+        <v>0</v>
+      </c>
+      <c r="V6" s="44" t="n">
+        <v>0</v>
+      </c>
+      <c r="W6" s="44" t="n">
+        <v>0</v>
+      </c>
       <c r="X6" s="44" t="n">
         <v>0</v>
       </c>
       <c r="Y6" s="44" t="n">
         <v>0</v>
       </c>
-      <c r="Z6" s="44" t="n">
-        <v>0</v>
-      </c>
-      <c r="AA6" s="44" t="n">
-        <v>0</v>
-      </c>
-      <c r="AB6" s="123" t="n">
+      <c r="Z6" s="123" t="n">
+        <v>0</v>
+      </c>
+      <c r="AA6" s="123" t="n">
+        <v>0</v>
+      </c>
+      <c r="AB6" s="43" t="n">
         <v>0</v>
       </c>
       <c r="AC6" s="123" t="n">
         <v>0</v>
       </c>
-      <c r="AD6" s="43" t="n">
-        <v>0</v>
-      </c>
+      <c r="AD6" s="123" t="n">
+        <v>0</v>
+      </c>
+      <c r="AE6" s="123" t="n"/>
+      <c r="AF6" s="123" t="n"/>
     </row>
     <row r="7" ht="20" customHeight="1" s="83">
       <c r="A7" s="41" t="inlineStr">
@@ -21043,35 +21215,41 @@
       <c r="S7" s="43" t="n">
         <v>0</v>
       </c>
-      <c r="T7" s="124" t="n">
-        <v>0</v>
-      </c>
-      <c r="U7" s="124" t="n">
-        <v>0</v>
-      </c>
-      <c r="V7" s="124" t="n"/>
-      <c r="W7" s="124" t="n"/>
+      <c r="T7" s="46" t="n">
+        <v>0</v>
+      </c>
+      <c r="U7" s="46" t="n">
+        <v>0</v>
+      </c>
+      <c r="V7" s="46" t="n">
+        <v>0</v>
+      </c>
+      <c r="W7" s="46" t="n">
+        <v>0</v>
+      </c>
       <c r="X7" s="46" t="n">
         <v>0</v>
       </c>
       <c r="Y7" s="46" t="n">
         <v>0</v>
       </c>
-      <c r="Z7" s="46" t="n">
-        <v>0</v>
-      </c>
-      <c r="AA7" s="46" t="n">
-        <v>0</v>
-      </c>
-      <c r="AB7" s="124" t="n">
+      <c r="Z7" s="124" t="n">
+        <v>0</v>
+      </c>
+      <c r="AA7" s="124" t="n">
+        <v>0</v>
+      </c>
+      <c r="AB7" s="43" t="n">
         <v>0</v>
       </c>
       <c r="AC7" s="124" t="n">
         <v>0</v>
       </c>
-      <c r="AD7" s="43" t="n">
-        <v>0</v>
-      </c>
+      <c r="AD7" s="124" t="n">
+        <v>0</v>
+      </c>
+      <c r="AE7" s="124" t="n"/>
+      <c r="AF7" s="124" t="n"/>
     </row>
     <row r="8" ht="20" customHeight="1" s="83">
       <c r="A8" s="41" t="inlineStr">
@@ -21133,35 +21311,41 @@
       <c r="S8" s="43" t="n">
         <v>0</v>
       </c>
-      <c r="T8" s="123" t="n">
-        <v>0</v>
-      </c>
-      <c r="U8" s="123" t="n">
-        <v>0</v>
-      </c>
-      <c r="V8" s="123" t="n"/>
-      <c r="W8" s="123" t="n"/>
+      <c r="T8" s="44" t="n">
+        <v>0</v>
+      </c>
+      <c r="U8" s="44" t="n">
+        <v>0</v>
+      </c>
+      <c r="V8" s="44" t="n">
+        <v>0</v>
+      </c>
+      <c r="W8" s="44" t="n">
+        <v>0</v>
+      </c>
       <c r="X8" s="44" t="n">
         <v>0</v>
       </c>
       <c r="Y8" s="44" t="n">
         <v>0</v>
       </c>
-      <c r="Z8" s="44" t="n">
-        <v>0</v>
-      </c>
-      <c r="AA8" s="44" t="n">
-        <v>0</v>
-      </c>
-      <c r="AB8" s="123" t="n">
+      <c r="Z8" s="123" t="n">
+        <v>0</v>
+      </c>
+      <c r="AA8" s="123" t="n">
+        <v>0</v>
+      </c>
+      <c r="AB8" s="43" t="n">
         <v>0</v>
       </c>
       <c r="AC8" s="123" t="n">
         <v>0</v>
       </c>
-      <c r="AD8" s="43" t="n">
-        <v>0</v>
-      </c>
+      <c r="AD8" s="123" t="n">
+        <v>0</v>
+      </c>
+      <c r="AE8" s="123" t="n"/>
+      <c r="AF8" s="123" t="n"/>
     </row>
     <row r="9" ht="20" customHeight="1" s="83">
       <c r="A9" s="41" t="inlineStr">
@@ -21223,35 +21407,41 @@
       <c r="S9" s="43" t="n">
         <v>0</v>
       </c>
-      <c r="T9" s="124" t="n">
-        <v>0</v>
-      </c>
-      <c r="U9" s="124" t="n">
-        <v>0</v>
-      </c>
-      <c r="V9" s="124" t="n"/>
-      <c r="W9" s="124" t="n"/>
+      <c r="T9" s="46" t="n">
+        <v>0</v>
+      </c>
+      <c r="U9" s="46" t="n">
+        <v>0</v>
+      </c>
+      <c r="V9" s="46" t="n">
+        <v>0</v>
+      </c>
+      <c r="W9" s="46" t="n">
+        <v>0</v>
+      </c>
       <c r="X9" s="46" t="n">
         <v>0</v>
       </c>
       <c r="Y9" s="46" t="n">
         <v>0</v>
       </c>
-      <c r="Z9" s="46" t="n">
-        <v>0</v>
-      </c>
-      <c r="AA9" s="46" t="n">
-        <v>0</v>
-      </c>
-      <c r="AB9" s="124" t="n">
+      <c r="Z9" s="124" t="n">
+        <v>0</v>
+      </c>
+      <c r="AA9" s="124" t="n">
+        <v>0</v>
+      </c>
+      <c r="AB9" s="43" t="n">
         <v>0</v>
       </c>
       <c r="AC9" s="124" t="n">
         <v>0</v>
       </c>
-      <c r="AD9" s="43" t="n">
-        <v>0</v>
-      </c>
+      <c r="AD9" s="124" t="n">
+        <v>0</v>
+      </c>
+      <c r="AE9" s="124" t="n"/>
+      <c r="AF9" s="124" t="n"/>
     </row>
     <row r="10" ht="20" customHeight="1" s="83">
       <c r="A10" s="47" t="inlineStr">
@@ -21313,35 +21503,41 @@
       <c r="S10" s="49" t="n">
         <v>0</v>
       </c>
-      <c r="T10" s="125" t="n">
-        <v>0</v>
-      </c>
-      <c r="U10" s="125" t="n">
-        <v>0</v>
-      </c>
-      <c r="V10" s="125" t="n"/>
-      <c r="W10" s="125" t="n"/>
+      <c r="T10" s="49" t="n">
+        <v>0</v>
+      </c>
+      <c r="U10" s="49" t="n">
+        <v>0</v>
+      </c>
+      <c r="V10" s="49" t="n">
+        <v>0</v>
+      </c>
+      <c r="W10" s="49" t="n">
+        <v>0</v>
+      </c>
       <c r="X10" s="49" t="n">
         <v>0</v>
       </c>
       <c r="Y10" s="49" t="n">
         <v>0</v>
       </c>
-      <c r="Z10" s="49" t="n">
-        <v>0</v>
-      </c>
-      <c r="AA10" s="49" t="n">
-        <v>0</v>
-      </c>
-      <c r="AB10" s="125" t="n">
+      <c r="Z10" s="125" t="n">
+        <v>0</v>
+      </c>
+      <c r="AA10" s="125" t="n">
+        <v>0</v>
+      </c>
+      <c r="AB10" s="49" t="n">
         <v>0</v>
       </c>
       <c r="AC10" s="125" t="n">
         <v>0</v>
       </c>
-      <c r="AD10" s="49" t="n">
-        <v>0</v>
-      </c>
+      <c r="AD10" s="125" t="n">
+        <v>0</v>
+      </c>
+      <c r="AE10" s="125" t="n"/>
+      <c r="AF10" s="125" t="n"/>
     </row>
     <row r="12" ht="26" customHeight="1" s="83">
       <c r="A12" s="72" t="n"/>
@@ -24012,7 +24208,7 @@
       <formula>0</formula>
     </cfRule>
   </conditionalFormatting>
-  <conditionalFormatting sqref="AD4:AD9">
+  <conditionalFormatting sqref="AB4:AB9">
     <cfRule type="cellIs" priority="75" operator="greaterThan" dxfId="3">
       <formula>0</formula>
     </cfRule>
@@ -24020,7 +24216,7 @@
       <formula>0</formula>
     </cfRule>
   </conditionalFormatting>
-  <conditionalFormatting sqref="AD4:AD10">
+  <conditionalFormatting sqref="AB4:AB10">
     <cfRule type="cellIs" priority="77" operator="greaterThan" dxfId="1">
       <formula>0</formula>
     </cfRule>
@@ -30526,51 +30722,61 @@
       <c r="S2" s="105" t="n"/>
       <c r="T2" s="105" t="inlineStr">
         <is>
+          <t>3PP搭售率(未加Care)</t>
+        </is>
+      </c>
+      <c r="U2" s="105" t="inlineStr">
+        <is>
+          <t>3PP搭售率(未加Care)</t>
+        </is>
+      </c>
+      <c r="V2" s="105" t="inlineStr">
+        <is>
+          <t>SA Care搭售率</t>
+        </is>
+      </c>
+      <c r="W2" s="105" t="inlineStr">
+        <is>
+          <t>SA Care搭售率</t>
+        </is>
+      </c>
+      <c r="X2" s="105" t="inlineStr">
+        <is>
+          <t>AC搭售率</t>
+        </is>
+      </c>
+      <c r="Y2" s="105" t="inlineStr">
+        <is>
+          <t>AC搭售率</t>
+        </is>
+      </c>
+      <c r="Z2" s="105" t="inlineStr">
+        <is>
+          <t>禮券金額</t>
+        </is>
+      </c>
+      <c r="AA2" s="105" t="n"/>
+      <c r="AB2" s="105" t="n"/>
+      <c r="AC2" s="105" t="inlineStr">
+        <is>
           <t>總業績差異</t>
         </is>
       </c>
-      <c r="U2" s="105" t="inlineStr">
+      <c r="AD2" s="105" t="inlineStr">
         <is>
           <t>3PP(未加SA Care)差異</t>
         </is>
       </c>
-      <c r="V2" s="105" t="inlineStr">
+      <c r="AE2" s="105" t="inlineStr">
         <is>
           <t>SA Care</t>
         </is>
       </c>
-      <c r="W2" s="105" t="inlineStr">
+      <c r="AF2" s="105" t="inlineStr">
         <is>
           <t>AC</t>
         </is>
       </c>
-      <c r="X2" s="105" t="inlineStr">
-        <is>
-          <t>3PP搭售率(未加Care)</t>
-        </is>
-      </c>
-      <c r="Y2" s="105" t="inlineStr">
-        <is>
-          <t>3PP搭售率(未加Care)</t>
-        </is>
-      </c>
-      <c r="Z2" s="105" t="inlineStr">
-        <is>
-          <t>SA Care搭售率</t>
-        </is>
-      </c>
-      <c r="AA2" s="105" t="inlineStr">
-        <is>
-          <t>SA Care搭售率</t>
-        </is>
-      </c>
-      <c r="AB2" s="105" t="inlineStr">
-        <is>
-          <t>禮券金額</t>
-        </is>
-      </c>
-      <c r="AC2" s="105" t="n"/>
-      <c r="AD2" s="105" t="n"/>
     </row>
     <row r="3" ht="42" customHeight="1" s="83">
       <c r="A3" s="86" t="n"/>
@@ -30664,10 +30870,26 @@
           <t>較上週比</t>
         </is>
       </c>
-      <c r="T3" s="86" t="n"/>
-      <c r="U3" s="86" t="n"/>
-      <c r="V3" s="86" t="n"/>
-      <c r="W3" s="86" t="n"/>
+      <c r="T3" s="39" t="inlineStr">
+        <is>
+          <t>W15</t>
+        </is>
+      </c>
+      <c r="U3" s="40" t="inlineStr">
+        <is>
+          <t>W16</t>
+        </is>
+      </c>
+      <c r="V3" s="39" t="inlineStr">
+        <is>
+          <t>W15</t>
+        </is>
+      </c>
+      <c r="W3" s="40" t="inlineStr">
+        <is>
+          <t>W16</t>
+        </is>
+      </c>
       <c r="X3" s="39" t="inlineStr">
         <is>
           <t>W15</t>
@@ -30688,21 +30910,15 @@
           <t>W16</t>
         </is>
       </c>
-      <c r="AB3" s="39" t="inlineStr">
-        <is>
-          <t>W15</t>
-        </is>
-      </c>
-      <c r="AC3" s="40" t="inlineStr">
-        <is>
-          <t>W16</t>
-        </is>
-      </c>
-      <c r="AD3" s="86" t="inlineStr">
+      <c r="AB3" s="86" t="inlineStr">
         <is>
           <t>較上週比</t>
         </is>
       </c>
+      <c r="AC3" s="86" t="n"/>
+      <c r="AD3" s="86" t="n"/>
+      <c r="AE3" s="86" t="n"/>
+      <c r="AF3" s="86" t="n"/>
     </row>
     <row r="4" ht="20" customHeight="1" s="83">
       <c r="A4" s="41" t="inlineStr">
@@ -30764,35 +30980,41 @@
       <c r="S4" s="43" t="n">
         <v>0</v>
       </c>
-      <c r="T4" s="123" t="n">
-        <v>0</v>
-      </c>
-      <c r="U4" s="123" t="n">
-        <v>0</v>
-      </c>
-      <c r="V4" s="123" t="n"/>
-      <c r="W4" s="123" t="n"/>
+      <c r="T4" s="44" t="n">
+        <v>0</v>
+      </c>
+      <c r="U4" s="44" t="n">
+        <v>0</v>
+      </c>
+      <c r="V4" s="44" t="n">
+        <v>0</v>
+      </c>
+      <c r="W4" s="44" t="n">
+        <v>0</v>
+      </c>
       <c r="X4" s="44" t="n">
         <v>0</v>
       </c>
       <c r="Y4" s="44" t="n">
         <v>0</v>
       </c>
-      <c r="Z4" s="44" t="n">
-        <v>0</v>
-      </c>
-      <c r="AA4" s="44" t="n">
-        <v>0</v>
-      </c>
-      <c r="AB4" s="123" t="n">
+      <c r="Z4" s="123" t="n">
+        <v>0</v>
+      </c>
+      <c r="AA4" s="123" t="n">
+        <v>0</v>
+      </c>
+      <c r="AB4" s="43" t="n">
         <v>0</v>
       </c>
       <c r="AC4" s="123" t="n">
         <v>0</v>
       </c>
-      <c r="AD4" s="43" t="n">
-        <v>0</v>
-      </c>
+      <c r="AD4" s="123" t="n">
+        <v>0</v>
+      </c>
+      <c r="AE4" s="123" t="n"/>
+      <c r="AF4" s="123" t="n"/>
     </row>
     <row r="5" ht="20" customHeight="1" s="83">
       <c r="A5" s="41" t="inlineStr">
@@ -30854,35 +31076,41 @@
       <c r="S5" s="43" t="n">
         <v>0</v>
       </c>
-      <c r="T5" s="124" t="n">
-        <v>0</v>
-      </c>
-      <c r="U5" s="124" t="n">
-        <v>0</v>
-      </c>
-      <c r="V5" s="124" t="n"/>
-      <c r="W5" s="124" t="n"/>
+      <c r="T5" s="46" t="n">
+        <v>0</v>
+      </c>
+      <c r="U5" s="46" t="n">
+        <v>0</v>
+      </c>
+      <c r="V5" s="46" t="n">
+        <v>0</v>
+      </c>
+      <c r="W5" s="46" t="n">
+        <v>0</v>
+      </c>
       <c r="X5" s="46" t="n">
         <v>0</v>
       </c>
       <c r="Y5" s="46" t="n">
         <v>0</v>
       </c>
-      <c r="Z5" s="46" t="n">
-        <v>0</v>
-      </c>
-      <c r="AA5" s="46" t="n">
-        <v>0</v>
-      </c>
-      <c r="AB5" s="124" t="n">
+      <c r="Z5" s="124" t="n">
+        <v>0</v>
+      </c>
+      <c r="AA5" s="124" t="n">
+        <v>0</v>
+      </c>
+      <c r="AB5" s="43" t="n">
         <v>0</v>
       </c>
       <c r="AC5" s="124" t="n">
         <v>0</v>
       </c>
-      <c r="AD5" s="43" t="n">
-        <v>0</v>
-      </c>
+      <c r="AD5" s="124" t="n">
+        <v>0</v>
+      </c>
+      <c r="AE5" s="124" t="n"/>
+      <c r="AF5" s="124" t="n"/>
     </row>
     <row r="6" ht="20" customHeight="1" s="83">
       <c r="A6" s="41" t="inlineStr">
@@ -30944,35 +31172,41 @@
       <c r="S6" s="43" t="n">
         <v>0</v>
       </c>
-      <c r="T6" s="123" t="n">
-        <v>0</v>
-      </c>
-      <c r="U6" s="123" t="n">
-        <v>0</v>
-      </c>
-      <c r="V6" s="123" t="n"/>
-      <c r="W6" s="123" t="n"/>
+      <c r="T6" s="44" t="n">
+        <v>0</v>
+      </c>
+      <c r="U6" s="44" t="n">
+        <v>0</v>
+      </c>
+      <c r="V6" s="44" t="n">
+        <v>0</v>
+      </c>
+      <c r="W6" s="44" t="n">
+        <v>0</v>
+      </c>
       <c r="X6" s="44" t="n">
         <v>0</v>
       </c>
       <c r="Y6" s="44" t="n">
         <v>0</v>
       </c>
-      <c r="Z6" s="44" t="n">
-        <v>0</v>
-      </c>
-      <c r="AA6" s="44" t="n">
-        <v>0</v>
-      </c>
-      <c r="AB6" s="123" t="n">
+      <c r="Z6" s="123" t="n">
+        <v>0</v>
+      </c>
+      <c r="AA6" s="123" t="n">
+        <v>0</v>
+      </c>
+      <c r="AB6" s="43" t="n">
         <v>0</v>
       </c>
       <c r="AC6" s="123" t="n">
         <v>0</v>
       </c>
-      <c r="AD6" s="43" t="n">
-        <v>0</v>
-      </c>
+      <c r="AD6" s="123" t="n">
+        <v>0</v>
+      </c>
+      <c r="AE6" s="123" t="n"/>
+      <c r="AF6" s="123" t="n"/>
     </row>
     <row r="7" ht="20" customHeight="1" s="83">
       <c r="A7" s="41" t="inlineStr">
@@ -31034,35 +31268,41 @@
       <c r="S7" s="43" t="n">
         <v>0</v>
       </c>
-      <c r="T7" s="124" t="n">
-        <v>0</v>
-      </c>
-      <c r="U7" s="124" t="n">
-        <v>0</v>
-      </c>
-      <c r="V7" s="124" t="n"/>
-      <c r="W7" s="124" t="n"/>
+      <c r="T7" s="46" t="n">
+        <v>0</v>
+      </c>
+      <c r="U7" s="46" t="n">
+        <v>0</v>
+      </c>
+      <c r="V7" s="46" t="n">
+        <v>0</v>
+      </c>
+      <c r="W7" s="46" t="n">
+        <v>0</v>
+      </c>
       <c r="X7" s="46" t="n">
         <v>0</v>
       </c>
       <c r="Y7" s="46" t="n">
         <v>0</v>
       </c>
-      <c r="Z7" s="46" t="n">
-        <v>0</v>
-      </c>
-      <c r="AA7" s="46" t="n">
-        <v>0</v>
-      </c>
-      <c r="AB7" s="124" t="n">
+      <c r="Z7" s="124" t="n">
+        <v>0</v>
+      </c>
+      <c r="AA7" s="124" t="n">
+        <v>0</v>
+      </c>
+      <c r="AB7" s="43" t="n">
         <v>0</v>
       </c>
       <c r="AC7" s="124" t="n">
         <v>0</v>
       </c>
-      <c r="AD7" s="43" t="n">
-        <v>0</v>
-      </c>
+      <c r="AD7" s="124" t="n">
+        <v>0</v>
+      </c>
+      <c r="AE7" s="124" t="n"/>
+      <c r="AF7" s="124" t="n"/>
     </row>
     <row r="8" ht="20" customHeight="1" s="83">
       <c r="A8" s="41" t="inlineStr">
@@ -31124,35 +31364,41 @@
       <c r="S8" s="43" t="n">
         <v>0</v>
       </c>
-      <c r="T8" s="123" t="n">
-        <v>0</v>
-      </c>
-      <c r="U8" s="123" t="n">
-        <v>0</v>
-      </c>
-      <c r="V8" s="123" t="n"/>
-      <c r="W8" s="123" t="n"/>
+      <c r="T8" s="44" t="n">
+        <v>0</v>
+      </c>
+      <c r="U8" s="44" t="n">
+        <v>0</v>
+      </c>
+      <c r="V8" s="44" t="n">
+        <v>0</v>
+      </c>
+      <c r="W8" s="44" t="n">
+        <v>0</v>
+      </c>
       <c r="X8" s="44" t="n">
         <v>0</v>
       </c>
       <c r="Y8" s="44" t="n">
         <v>0</v>
       </c>
-      <c r="Z8" s="44" t="n">
-        <v>0</v>
-      </c>
-      <c r="AA8" s="44" t="n">
-        <v>0</v>
-      </c>
-      <c r="AB8" s="123" t="n">
+      <c r="Z8" s="123" t="n">
+        <v>0</v>
+      </c>
+      <c r="AA8" s="123" t="n">
+        <v>0</v>
+      </c>
+      <c r="AB8" s="43" t="n">
         <v>0</v>
       </c>
       <c r="AC8" s="123" t="n">
         <v>0</v>
       </c>
-      <c r="AD8" s="43" t="n">
-        <v>0</v>
-      </c>
+      <c r="AD8" s="123" t="n">
+        <v>0</v>
+      </c>
+      <c r="AE8" s="123" t="n"/>
+      <c r="AF8" s="123" t="n"/>
     </row>
     <row r="9" ht="20" customHeight="1" s="83">
       <c r="A9" s="41" t="inlineStr">
@@ -31214,35 +31460,41 @@
       <c r="S9" s="43" t="n">
         <v>0</v>
       </c>
-      <c r="T9" s="124" t="n">
-        <v>0</v>
-      </c>
-      <c r="U9" s="124" t="n">
-        <v>0</v>
-      </c>
-      <c r="V9" s="124" t="n"/>
-      <c r="W9" s="124" t="n"/>
+      <c r="T9" s="46" t="n">
+        <v>0</v>
+      </c>
+      <c r="U9" s="46" t="n">
+        <v>0</v>
+      </c>
+      <c r="V9" s="46" t="n">
+        <v>0</v>
+      </c>
+      <c r="W9" s="46" t="n">
+        <v>0</v>
+      </c>
       <c r="X9" s="46" t="n">
         <v>0</v>
       </c>
       <c r="Y9" s="46" t="n">
         <v>0</v>
       </c>
-      <c r="Z9" s="46" t="n">
-        <v>0</v>
-      </c>
-      <c r="AA9" s="46" t="n">
-        <v>0</v>
-      </c>
-      <c r="AB9" s="124" t="n">
+      <c r="Z9" s="124" t="n">
+        <v>0</v>
+      </c>
+      <c r="AA9" s="124" t="n">
+        <v>0</v>
+      </c>
+      <c r="AB9" s="43" t="n">
         <v>0</v>
       </c>
       <c r="AC9" s="124" t="n">
         <v>0</v>
       </c>
-      <c r="AD9" s="43" t="n">
-        <v>0</v>
-      </c>
+      <c r="AD9" s="124" t="n">
+        <v>0</v>
+      </c>
+      <c r="AE9" s="124" t="n"/>
+      <c r="AF9" s="124" t="n"/>
     </row>
     <row r="10" ht="20" customHeight="1" s="83">
       <c r="A10" s="47" t="inlineStr">
@@ -31304,35 +31556,41 @@
       <c r="S10" s="49" t="n">
         <v>0</v>
       </c>
-      <c r="T10" s="125" t="n">
-        <v>0</v>
-      </c>
-      <c r="U10" s="125" t="n">
-        <v>0</v>
-      </c>
-      <c r="V10" s="125" t="n"/>
-      <c r="W10" s="125" t="n"/>
+      <c r="T10" s="49" t="n">
+        <v>0</v>
+      </c>
+      <c r="U10" s="49" t="n">
+        <v>0</v>
+      </c>
+      <c r="V10" s="49" t="n">
+        <v>0</v>
+      </c>
+      <c r="W10" s="49" t="n">
+        <v>0</v>
+      </c>
       <c r="X10" s="49" t="n">
         <v>0</v>
       </c>
       <c r="Y10" s="49" t="n">
         <v>0</v>
       </c>
-      <c r="Z10" s="49" t="n">
-        <v>0</v>
-      </c>
-      <c r="AA10" s="49" t="n">
-        <v>0</v>
-      </c>
-      <c r="AB10" s="125" t="n">
+      <c r="Z10" s="125" t="n">
+        <v>0</v>
+      </c>
+      <c r="AA10" s="125" t="n">
+        <v>0</v>
+      </c>
+      <c r="AB10" s="49" t="n">
         <v>0</v>
       </c>
       <c r="AC10" s="125" t="n">
         <v>0</v>
       </c>
-      <c r="AD10" s="49" t="n">
-        <v>0</v>
-      </c>
+      <c r="AD10" s="125" t="n">
+        <v>0</v>
+      </c>
+      <c r="AE10" s="125" t="n"/>
+      <c r="AF10" s="125" t="n"/>
     </row>
     <row r="12" ht="26" customHeight="1" s="83">
       <c r="A12" s="72" t="n"/>
@@ -33989,7 +34247,7 @@
       <formula>0</formula>
     </cfRule>
   </conditionalFormatting>
-  <conditionalFormatting sqref="AD4:AD9">
+  <conditionalFormatting sqref="AB4:AB9">
     <cfRule type="cellIs" priority="87" operator="greaterThan" dxfId="3">
       <formula>0</formula>
     </cfRule>
@@ -33997,7 +34255,7 @@
       <formula>0</formula>
     </cfRule>
   </conditionalFormatting>
-  <conditionalFormatting sqref="AD4:AD10">
+  <conditionalFormatting sqref="AB4:AB10">
     <cfRule type="cellIs" priority="89" operator="greaterThan" dxfId="1">
       <formula>0</formula>
     </cfRule>
